--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_FCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_FCP.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,10 +448,10 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,67 +590,67 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="D2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E2" t="n">
+        <v>174</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>50.7%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>92</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>55.4%</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>56</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>37.8%</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>44</v>
       </c>
-      <c r="E2" t="n">
-        <v>99</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>57.9%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>48</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>68.8%</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>39.3%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>36.8%</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>38.6%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>31</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>80.6%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -663,10 +663,10 @@
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -681,28 +681,216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>attempts</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>made</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pps</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>zone_share</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>FCP_T._BROPLEH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>T. Bropleh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:K4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -740,7 +928,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: T. Bropleh (14 L)</t>
+          <t>Maior volume: C. Allen Williams (26 L)</t>
         </is>
       </c>
     </row>
@@ -752,7 +940,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: T. Bropleh (8 3PA)</t>
+          <t>Maior volume 3pt: T. Bropleh (13 3PA)</t>
         </is>
       </c>
     </row>
@@ -764,7 +952,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: T. Bropleh (1.7 pts/shot)</t>
+          <t>Mais eficaz: T. Bropleh (1.6 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -776,7 +964,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Restricted Area (31 L)</t>
+          <t>Zona mais usada: Above the Break 3 (44 L)</t>
         </is>
       </c>
     </row>
@@ -788,7 +976,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (80.6%)</t>
+          <t>Zona mais eficaz: Restricted Area (78.6%)</t>
         </is>
       </c>
     </row>
@@ -804,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -928,141 +1116,141 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>8</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
         <v>6</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>11</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>3</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -1073,10 +1261,10 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1091,69 +1279,69 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1168,55 +1356,55 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D5" t="n">
         <v>9</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1227,35 +1415,35 @@
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FCP_T._OMLID</t>
+          <t>FCP_M._QUEIROZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
         <v>8</v>
       </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1263,16 +1451,16 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1284,100 +1472,104 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FCP_M._QUEIROZ</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
         <v>7</v>
       </c>
-      <c r="D7" t="n">
-        <v>6</v>
-      </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1386,78 +1578,78 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FCP_V._VOYTSO</t>
+          <t>FCP_J._WOODARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>4</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>2</v>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1472,21 +1664,21 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1495,11 +1687,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1507,7 +1699,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1516,22 +1708,22 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S9" t="n">
         <v>6</v>
@@ -1540,22 +1732,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FCP_G._DELGADO</t>
+          <t>FCP_T._OMLID</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>T. Omlid</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="n">
         <v>4</v>
       </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,12 +1755,16 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1580,20 +1776,20 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1604,14 +1800,91 @@
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FCP_V._VOYTSO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V. Voytso</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:S11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1622,7 +1895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1755,33 +2028,33 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1790,11 +2063,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1814,133 +2087,133 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_M._QUEIROZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H4" t="n">
         <v>10</v>
       </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1948,34 +2221,342 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FCP_G._DELGADO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>G. Delgado</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>26</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>8</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S4"/>
+  <autoFilter ref="A1:S8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1986,7 +2567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2089,29 +2670,29 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2119,55 +2700,55 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2179,167 +2760,167 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_V._VOYTSO</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_C._DUNDAO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>3</v>
-      </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_J._WOODARD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
         <v>11</v>
-      </c>
-      <c r="H6" t="n">
-        <v>10</v>
       </c>
       <c r="I6" t="n">
         <v>0.9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -2347,55 +2928,55 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FCP_A._BESSA</t>
+          <t>FCP_V._VOYTSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Bessa</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2403,70 +2984,70 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FCP_T._OMLID</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
         <v>6</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -2481,25 +3062,29 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -2517,7 +3102,9 @@
       <c r="M9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2531,25 +3118,29 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -2557,7 +3148,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -2567,10 +3158,68 @@
       <c r="M10" t="n">
         <v>8</v>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FCP_T._OMLID</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T. Omlid</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2581,28 +3230,211 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>three_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>shot_attempts</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>points_from_shots</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pts_per_shot</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>top_zone_1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_volume</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>FCP_T._BROPLEH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>T. Bropleh</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H2" t="n">
+        <v>38</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FCP_X._WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H3" t="n">
+        <v>23</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:N3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2677,71 +3509,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2751,32 +3583,32 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -2786,13 +3618,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2804,14 +3636,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2821,25 +3653,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2856,32 +3688,32 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2896,7 +3728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3002,82 +3834,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>5</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3086,57 +3918,57 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="4">
@@ -3152,61 +3984,61 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="J4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
@@ -3226,68 +4058,68 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="n">
+        <v>19</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>9</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FCP_T._OMLID</t>
+          <t>FCP_M._QUEIROZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3300,64 +4132,64 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>12</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>8</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FCP_M._QUEIROZ</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3366,113 +4198,127 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="P7" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FCP_V._VOYTSO</t>
+          <t>FCP_J._WOODARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
@@ -3492,7 +4338,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3501,40 +4347,40 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -3542,18 +4388,18 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FCP_G._DELGADO</t>
+          <t>FCP_T._OMLID</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>T. Omlid</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3562,47 +4408,131 @@
         </is>
       </c>
       <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FCP_V._VOYTSO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V. Voytso</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>1</v>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3613,7 +4543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3689,84 +4619,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FCP_M._QUEIROZ</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FCP_T._OMLID</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -3779,12 +4709,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3793,25 +4723,25 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>6</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>9</v>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -3824,12 +4754,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3838,13 +4768,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3856,11 +4786,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -3879,85 +4809,400 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>FCP_M._QUEIROZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M. Queiroz</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FCP_T._OMLID</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>T. Omlid</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FCP_T._BROPLEH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T. Bropleh</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FCP_X._WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>C. Allen Williams</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
+      <c r="K14" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K7"/>
+  <autoFilter ref="A1:K14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_FCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_FCP.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>148</v>
+        <v>214</v>
       </c>
       <c r="D2" t="n">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E2" t="n">
-        <v>174</v>
+        <v>247</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,27 +646,27 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
         <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -757,46 +757,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_M._QUEIROZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -816,17 +816,17 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -834,25 +834,25 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -861,25 +861,25 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" t="n">
         <v>8</v>
       </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -889,8 +889,188 @@
         <v>2</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FCP_A._BESSA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A. Bessa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>68.8%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:K8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -928,7 +1108,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: C. Allen Williams (26 L)</t>
+          <t>Maior volume: C. Allen Williams (40 L)</t>
         </is>
       </c>
     </row>
@@ -940,7 +1120,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: T. Bropleh (13 3PA)</t>
+          <t>Maior volume 3pt: T. Bropleh (17 3PA)</t>
         </is>
       </c>
     </row>
@@ -952,7 +1132,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: T. Bropleh (1.6 pts/shot)</t>
+          <t>Mais eficaz: V. Voytso (1.8 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -964,7 +1144,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (44 L)</t>
+          <t>Zona mais usada: Above the Break 3 (68 L)</t>
         </is>
       </c>
     </row>
@@ -976,7 +1156,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (78.6%)</t>
+          <t>Zona mais eficaz: Restricted Area (78.0%)</t>
         </is>
       </c>
     </row>
@@ -992,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1125,59 +1305,59 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>15</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>10</v>
       </c>
-      <c r="E2" t="n">
-        <v>22</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>38.5%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>34.6%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>8</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1187,7 +1367,7 @@
         <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1202,34 +1382,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1237,11 +1417,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1250,7 +1430,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -1261,7 +1441,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -1270,43 +1450,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1314,16 +1494,16 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -1331,7 +1511,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1341,32 +1521,32 @@
         <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_C._DUNDAO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1374,16 +1554,16 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1391,34 +1571,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1433,17 +1613,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1456,11 +1636,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1468,24 +1648,24 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>90.9%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>6</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1501,55 +1681,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FCP_G._DELGADO</t>
+          <t>FCP_J._WOODARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1558,63 +1738,63 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FCP_J._WOODARD</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>11</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1622,153 +1802,153 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
         <v>4</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>5</v>
-      </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FCP_A._BESSA</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Bessa</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>4</v>
       </c>
-      <c r="E9" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>3</v>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FCP_T._OMLID</t>
+          <t>FCP_V._VOYTSO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1776,93 +1956,93 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>9</v>
       </c>
       <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>7</v>
-      </c>
-      <c r="S10" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FCP_V._VOYTSO</t>
+          <t>FCP_J._GUERREIRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>J. Guerreiro</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
         <v>4</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1877,14 +2057,91 @@
         <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FCP_T._OMLID</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T. Omlid</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
         <v>6</v>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>10</v>
+      </c>
+      <c r="R12" t="n">
+        <v>9</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S11"/>
+  <autoFilter ref="A1:S12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1895,7 +2152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1911,7 +2168,7 @@
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
@@ -2019,75 +2276,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_V._VOYTSO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -2105,21 +2362,21 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -2131,7 +2388,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2140,24 +2397,24 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>90.9%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>6</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>4</v>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -2173,42 +2430,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2217,31 +2474,31 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -2250,12 +2507,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_G._DELGADO</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2263,119 +2520,119 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>11</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>7</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FCP_J._WOODARD</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -2388,17 +2645,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -2413,59 +2670,59 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
+        <v>18</v>
+      </c>
+      <c r="G7" t="n">
+        <v>42</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>15</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>10</v>
       </c>
-      <c r="G7" t="n">
-        <v>22</v>
-      </c>
-      <c r="H7" t="n">
-        <v>9</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>34.6%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>8</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>8</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -2475,48 +2732,48 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2525,16 +2782,16 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -2542,7 +2799,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -2552,11 +2809,165 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
         <v>6</v>
       </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>26.9%</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>26</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>15</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S8"/>
+  <autoFilter ref="A1:S10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2567,7 +2978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2670,29 +3081,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2700,55 +3111,55 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H3" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2756,7 +3167,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -2767,100 +3178,100 @@
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2868,55 +3279,55 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FCP_J._WOODARD</t>
+          <t>FCP_C._DUNDAO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2924,130 +3335,130 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FCP_V._VOYTSO</t>
+          <t>FCP_J._WOODARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H7" t="n">
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FCP_A._BESSA</t>
+          <t>FCP_V._VOYTSO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A. Bessa</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N8" t="n">
         <v>2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>9</v>
-      </c>
-      <c r="H8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>6</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3074,17 +3485,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H9" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -3092,11 +3503,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -3109,38 +3520,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FCP_G._DELGADO</t>
+          <t>FCP_J._GUERREIRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>J. Guerreiro</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -3148,29 +3559,29 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FCP_T._OMLID</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3186,17 +3597,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -3204,11 +3615,11 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -3218,8 +3629,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FCP_T._OMLID</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T. Omlid</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N11"/>
+  <autoFilter ref="A1:N12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3230,11 +3697,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -3333,29 +3800,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3363,52 +3830,52 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="n">
         <v>19</v>
-      </c>
-      <c r="H3" t="n">
-        <v>23</v>
       </c>
       <c r="I3" t="n">
         <v>1.2</v>
@@ -3419,22 +3886,190 @@
         </is>
       </c>
       <c r="K3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FCP_X._WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>51.9%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H4" t="n">
+        <v>28</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
         <v>5</v>
       </c>
-      <c r="L3" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="G5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" t="n">
+        <v>42</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>2</v>
       </c>
-      <c r="N3" t="n">
-        <v>3</v>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>26</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3513,17 +4148,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3531,14 +4166,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -3548,17 +4183,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3566,7 +4201,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -3583,32 +4218,32 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -3618,32 +4253,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3653,7 +4288,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
@@ -3663,22 +4298,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3688,32 +4323,32 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3728,7 +4363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3844,61 +4479,61 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="3">
@@ -3918,11 +4553,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3931,7 +4566,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -3944,42 +4579,42 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3988,16 +4623,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -4005,51 +4640,51 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_C._DUNDAO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4058,45 +4693,45 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -4104,11 +4739,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6">
@@ -4128,24 +4763,24 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>90.9%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>6</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4162,11 +4797,11 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -4178,88 +4813,88 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FCP_G._DELGADO</t>
+          <t>FCP_J._WOODARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FCP_J._WOODARD</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4268,33 +4903,33 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -4302,104 +4937,104 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FCP_A._BESSA</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Bessa</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FCP_T._OMLID</t>
+          <t>FCP_V._VOYTSO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4408,86 +5043,86 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FCP_V._VOYTSO</t>
+          <t>FCP_J._GUERREIRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>J. Guerreiro</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4512,27 +5147,97 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FCP_T._OMLID</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T. Omlid</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>6</v>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>2.7</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P11"/>
+  <autoFilter ref="A1:P12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4543,7 +5248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4619,12 +5324,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4633,160 +5338,160 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" t="n">
         <v>8</v>
       </c>
-      <c r="E3" t="n">
-        <v>5</v>
-      </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_M._QUEIROZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_G._DELGADO</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -4799,147 +5504,147 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FCP_M._QUEIROZ</t>
+          <t>FCP_C._DUNDAO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FCP_T._OMLID</t>
+          <t>FCP_J._WOODARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8</v>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4948,13 +5653,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -4966,11 +5671,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -4979,39 +5684,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -5024,12 +5729,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5038,29 +5743,29 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>17.5%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>3</v>
-      </c>
-      <c r="F11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -5069,140 +5774,365 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_C._DUNDAO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FCP_J._WOODARD</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>17.5%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
         <v>3</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_T._OMLID</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>T. Omlid</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FCP_M._QUEIROZ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M. Queiroz</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FCP_X._WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>19.2%</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
         <v>3</v>
       </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FCP_X._WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_FCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_FCP.xlsx
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,42 +590,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>214</v>
+        <v>285</v>
       </c>
       <c r="D2" t="n">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="E2" t="n">
-        <v>247</v>
+        <v>326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,27 +646,27 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
         <v>2</v>
       </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -802,129 +802,129 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_A._BESSA</t>
+          <t>FCP_T._OMLID</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Bessa</t>
+          <t>T. Omlid</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -947,21 +947,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -969,25 +969,25 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FCP_J._WOODARD</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -996,81 +996,441 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>FCP_T._BROPLEH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>T. Bropleh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>27</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>45.9%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>FCP_C._DUNDAO</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>C. Dundao</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>26.5%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>21</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FCP_X._WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
         <v>9</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>24.2%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FCP_X._WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>34.6%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>24.2%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
         <v>3</v>
       </c>
+      <c r="F13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>32.4%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FCP_G._DELGADO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>G. Delgado</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K8"/>
+  <autoFilter ref="A1:K16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1108,7 +1468,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: C. Allen Williams (40 L)</t>
+          <t>Maior volume: C. Allen Williams (48 L)</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: T. Bropleh (17 3PA)</t>
+          <t>Maior volume 3pt: T. Bropleh (20 3PA)</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1492,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: V. Voytso (1.8 pts/shot)</t>
+          <t>Mais eficaz: V. Voytso (1.7 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1504,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (68 L)</t>
+          <t>Zona mais usada: Above the Break 3 (95 L)</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1516,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (78.0%)</t>
+          <t>Zona mais eficaz: Restricted Area (77.3%)</t>
         </is>
       </c>
     </row>
@@ -1305,46 +1665,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>18</v>
       </c>
-      <c r="E2" t="n">
-        <v>42</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>45.0%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>16</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>15</v>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1353,21 +1713,21 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1382,46 +1742,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>54.1%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>17</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>52.9%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>54.8%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>14</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>57.1%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1441,7 +1801,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -1450,43 +1810,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_C._DUNDAO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1494,76 +1854,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1571,24 +1931,24 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1598,32 +1958,32 @@
         <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FCP_M._QUEIROZ</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1631,16 +1991,16 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1648,11 +2008,11 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1661,21 +2021,21 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -1690,34 +2050,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1725,11 +2085,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1738,21 +2098,21 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1767,30 +2127,30 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1802,11 +2162,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1826,7 +2186,7 @@
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1835,47 +2195,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FCP_G._DELGADO</t>
+          <t>FCP_V._VOYTSO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>19</v>
+      </c>
+      <c r="D9" t="n">
         <v>12</v>
       </c>
-      <c r="D9" t="n">
-        <v>7</v>
-      </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1883,107 +2243,107 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FCP_V._VOYTSO</t>
+          <t>FCP_M._QUEIROZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>19</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E10" t="n">
+        <v>29</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>73.7%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>90.9%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
         <v>10</v>
-      </c>
-      <c r="D10" t="n">
-        <v>7</v>
-      </c>
-      <c r="E10" t="n">
-        <v>18</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>70.0%</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>70.0%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>9</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1998,34 +2358,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -2033,31 +2393,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>8</v>
@@ -2075,69 +2435,69 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
         <v>8</v>
       </c>
-      <c r="D12" t="n">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" t="n">
         <v>6</v>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>10</v>
-      </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>9</v>
-      </c>
-      <c r="S12" t="n">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2152,7 +2512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2168,7 +2528,7 @@
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
@@ -2285,46 +2645,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>78.9%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>7</v>
       </c>
-      <c r="G2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>70.0%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>3</v>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -2333,18 +2693,18 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -2421,7 +2781,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -2430,166 +2790,166 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_J._GUERREIRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>J. Guerreiro</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>14</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_A._BESSA</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Bessa</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G5" t="n">
+        <v>48</v>
+      </c>
+      <c r="H5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>54.1%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>17</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>7</v>
       </c>
-      <c r="G5" t="n">
-        <v>19</v>
-      </c>
-      <c r="H5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>68.8%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>11</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FCP_G._DELGADO</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2597,183 +2957,183 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>13</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>7</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_T._OMLID</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>T. Omlid</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>15</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_J._WOODARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
+        <v>23</v>
+      </c>
+      <c r="H8" t="n">
         <v>11</v>
       </c>
-      <c r="G8" t="n">
-        <v>28</v>
-      </c>
-      <c r="H8" t="n">
-        <v>14</v>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2782,75 +3142,75 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>6</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>5</v>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FCP_J._WOODARD</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2859,31 +3219,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>7</v>
@@ -2892,42 +3252,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2936,24 +3296,24 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -2963,11 +3323,165 @@
         <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FCP_G._DELGADO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>G. Delgado</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>48.1%</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F11" t="n">
+        <v>13</v>
+      </c>
+      <c r="G11" t="n">
+        <v>26</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>16</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>81.2%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>9</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>32.4%</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>34</v>
+      </c>
+      <c r="F12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>38.2%</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:S12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3081,41 +3595,41 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>54.1%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>37</v>
+      </c>
+      <c r="H2" t="n">
+        <v>48</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>17</v>
       </c>
-      <c r="D2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>52.9%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>54.8%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>31</v>
-      </c>
-      <c r="H2" t="n">
-        <v>45</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>14</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -3137,29 +3651,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H3" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3167,18 +3681,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -3193,26 +3707,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -3223,11 +3737,11 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -3240,38 +3754,38 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_A._BESSA</t>
+          <t>FCP_V._VOYTSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Bessa</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -3279,55 +3793,55 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -3335,55 +3849,55 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FCP_J._WOODARD</t>
+          <t>FCP_C._DUNDAO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -3391,111 +3905,111 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FCP_V._VOYTSO</t>
+          <t>FCP_J._WOODARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>21</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>10</v>
       </c>
-      <c r="H8" t="n">
-        <v>18</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FCP_M._QUEIROZ</t>
+          <t>FCP_J._GUERREIRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>J. Guerreiro</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H9" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -3503,111 +4017,111 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FCP_J._GUERREIRO</t>
+          <t>FCP_T._OMLID</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Guerreiro</t>
+          <t>T. Omlid</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>13</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>8</v>
       </c>
-      <c r="H10" t="n">
-        <v>13</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>75.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FCP_G._DELGADO</t>
+          <t>FCP_M._QUEIROZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -3615,29 +4129,29 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FCP_T._OMLID</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3653,14 +4167,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -3671,18 +4185,18 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -3697,7 +4211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3791,38 +4305,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_V._VOYTSO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H2" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3830,55 +4344,55 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FCP_A._BESSA</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Bessa</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H3" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3886,55 +4400,55 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -3942,134 +4456,246 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>48.5%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>33</v>
+      </c>
+      <c r="H5" t="n">
+        <v>33</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>37.5%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>40</v>
-      </c>
-      <c r="H5" t="n">
-        <v>42</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>15</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>48</v>
+      </c>
+      <c r="H6" t="n">
+        <v>49</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>18</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>52.4%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H7" t="n">
+        <v>23</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>FCP_C._DUNDAO</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>C. Dundao</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>38.2%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>34</v>
+      </c>
+      <c r="H8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>11</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" t="n">
         <v>10</v>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>10.0%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>38.5%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>26</v>
-      </c>
-      <c r="H6" t="n">
-        <v>15</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>9</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N6"/>
+  <autoFilter ref="A1:N8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4148,32 +4774,32 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -4183,25 +4809,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C3" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D3" t="n">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -4218,32 +4844,32 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -4253,21 +4879,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -4278,7 +4904,7 @@
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -4288,25 +4914,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -4323,13 +4949,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4348,7 +4974,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4483,11 +5109,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4496,11 +5122,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4509,31 +5135,31 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -4553,11 +5179,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4579,42 +5205,42 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>37</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>51.4%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>31</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>58.1%</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>17</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>52.9%</t>
-        </is>
-      </c>
       <c r="P3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_C._DUNDAO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4623,68 +5249,68 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4693,29 +5319,29 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -4723,38 +5349,38 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FCP_M._QUEIROZ</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4763,11 +5389,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4776,11 +5402,11 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4793,15 +5419,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -4809,11 +5435,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -4833,11 +5459,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4846,11 +5472,11 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -4859,7 +5485,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4867,23 +5493,23 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
@@ -4903,11 +5529,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4937,19 +5563,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -4959,17 +5585,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FCP_G._DELGADO</t>
+          <t>FCP_V._VOYTSO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -4977,64 +5603,64 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L9" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FCP_V._VOYTSO</t>
+          <t>FCP_M._QUEIROZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5043,57 +5669,57 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>90.9%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
@@ -5113,57 +5739,57 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -5183,11 +5809,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -5196,44 +5822,44 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -5248,7 +5874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5338,17 +5964,17 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -5383,25 +6009,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -5414,12 +6040,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FCP_M._QUEIROZ</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5428,25 +6054,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -5473,25 +6099,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -5518,17 +6144,17 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -5549,57 +6175,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_M._QUEIROZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FCP_J._WOODARD</t>
+          <t>FCP_C._DUNDAO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5608,7 +6234,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -5618,334 +6244,334 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FCP_G._DELGADO</t>
+          <t>FCP_J._WOODARD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
         <v>2</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>58.3%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_C._DUNDAO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
         <v>3</v>
       </c>
-      <c r="F12" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>26.9%</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_T._OMLID</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>T. Omlid</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FCP_T._OMLID</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FCP_M._QUEIROZ</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
         <v>6</v>
       </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
@@ -5954,57 +6580,57 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
         <v>2</v>
       </c>
-      <c r="F16" t="n">
-        <v>6</v>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6013,29 +6639,29 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -6044,43 +6670,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FCP_J._WOODARD</t>
+          <t>FCP_V._VOYTSO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="n">
-        <v>3</v>
-      </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -6089,50 +6715,410 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20.6%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FCP_M._QUEIROZ</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>M. Queiroz</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FCP_T._BROPLEH</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>T. Bropleh</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FCP_J._GUERREIRO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>J. Guerreiro</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FCP_V._VOYTSO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>V. Voytso</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>9</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FCP_J._GUERREIRO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>J. Guerreiro</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>X. Williams</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D27" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>14.7%</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
         <v>4</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>18.5%</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
+      <c r="K27" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K19"/>
+  <autoFilter ref="A1:K27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>